--- a/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.931923711897442</v>
+        <v>0.0292958291171192</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4144450890952857</v>
+        <v>0.5450817913145818</v>
       </c>
       <c r="D2" t="n">
-        <v>1.517478622802156</v>
+        <v>0.5157859621974625</v>
       </c>
       <c r="E2" t="n">
-        <v>366.1470874500507</v>
+        <v>94.62542510428277</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8231979229714561</v>
+        <v>0.1755654355500955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4233251953041628</v>
+        <v>0.5938547655757322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3998727276672933</v>
+        <v>0.4182893300256367</v>
       </c>
       <c r="E3" t="n">
-        <v>94.45994051452128</v>
+        <v>70.43630097337221</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8886989878349163</v>
+        <v>0.5070287583756727</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5456021974051721</v>
+        <v>0.01682308027031189</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3430967904297442</v>
+        <v>0.4902056781053609</v>
       </c>
       <c r="E4" t="n">
-        <v>62.88405583069078</v>
+        <v>2913.887767452664</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1611912041708824</v>
+        <v>0.350199230737578</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07723827030555726</v>
+        <v>0.05559015057568738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08395293386532517</v>
+        <v>0.2946090801618906</v>
       </c>
       <c r="E5" t="n">
-        <v>108.6934411311963</v>
+        <v>529.9663287667713</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1838487663683674</v>
+        <v>0.6356219820564267</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02661466161857194</v>
+        <v>0.06824516281968585</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1572341047497955</v>
+        <v>0.5673768192367409</v>
       </c>
       <c r="E6" t="n">
-        <v>590.7800256986028</v>
+        <v>831.3802704754874</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1965041918748416</v>
+        <v>0.9380033154877552</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0626145081571724</v>
+        <v>0.07107668011768763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1338896837176692</v>
+        <v>0.8669266353700675</v>
       </c>
       <c r="E7" t="n">
-        <v>213.831726317461</v>
+        <v>1219.706145439861</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4674149315109892</v>
+        <v>0.6790205723408407</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1399634643830749</v>
+        <v>0.2370728179437773</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3274514671279143</v>
+        <v>0.4419477543970634</v>
       </c>
       <c r="E8" t="n">
-        <v>233.9549600113438</v>
+        <v>186.4185688727389</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3410480705972492</v>
+        <v>0.1015459074801979</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09441578290768561</v>
+        <v>0.1226594009302523</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2466322876895636</v>
+        <v>0.02111349345005446</v>
       </c>
       <c r="E9" t="n">
-        <v>261.2193428832832</v>
+        <v>17.21310661060557</v>
       </c>
     </row>
     <row r="10">
@@ -614,149 +614,92 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3734176115930888</v>
+        <v>0.159709008950557</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0764083521975765</v>
+        <v>0.02702034973559005</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2970092593955124</v>
+        <v>0.1326886592149669</v>
       </c>
       <c r="E10" t="n">
-        <v>388.7130802500578</v>
+        <v>491.0693625856185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kappa_p1</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.080931502256719</v>
+        <v>0.3253835697184519</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5144450890952857</v>
+        <v>0.03192636358403752</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5664864131614328</v>
+        <v>0.2934572061344145</v>
       </c>
       <c r="E11" t="n">
-        <v>110.1160114401457</v>
+        <v>919.1689036616015</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kappa_p2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7207077651182705</v>
+        <v>0.06115211922877228</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5233251953041629</v>
+        <v>0.07680834807784448</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1973825698141076</v>
+        <v>0.0156562288490722</v>
       </c>
       <c r="E12" t="n">
-        <v>37.71700112764235</v>
+        <v>20.38349898269491</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kappa_p3</t>
+          <t>lambda3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8311772563629507</v>
+        <v>-0.02682549469705131</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6456021974051721</v>
+        <v>0.01020283384938109</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1855750589577786</v>
+        <v>0.0370283285464324</v>
       </c>
       <c r="E13" t="n">
-        <v>28.74448998216683</v>
+        <v>362.9219988589598</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>theta_p1</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7972198290633489</v>
+        <v>0.004225746978660266</v>
       </c>
       <c r="C14" t="n">
-        <v>0.08723827030555725</v>
+        <v>0.004485641729012531</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7099815587577916</v>
+        <v>0.0002598947503522648</v>
       </c>
       <c r="E14" t="n">
-        <v>813.8418566427771</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>theta_p2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.8668599433940785</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.03661466161857194</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.8302452817755065</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2267.521383713632</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>theta_p3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.7085268635397205</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.07261450815717239</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.6359123553825481</v>
-      </c>
-      <c r="E16" t="n">
-        <v>875.7373306256247</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.570674236715234</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0089565171429642</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.56171771957227</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17436.6630984353</v>
+        <v>5.793925731324022</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0292958291171192</v>
+        <v>0.2697271548074719</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5450817913145818</v>
+        <v>0.3107473177365188</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5157859621974625</v>
+        <v>0.04102016292904687</v>
       </c>
       <c r="E2" t="n">
-        <v>94.62542510428277</v>
+        <v>13.20048817406935</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1755654355500955</v>
+        <v>0.7147919720935522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5938547655757322</v>
+        <v>0.4570885838847862</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4182893300256367</v>
+        <v>0.2577033882087659</v>
       </c>
       <c r="E3" t="n">
-        <v>70.43630097337221</v>
+        <v>56.37930967747001</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5070287583756727</v>
+        <v>0.9648840427475359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01682308027031189</v>
+        <v>0.7823380276949019</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4902056781053609</v>
+        <v>0.182546015052634</v>
       </c>
       <c r="E4" t="n">
-        <v>2913.887767452664</v>
+        <v>23.33339408164673</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.350199230737578</v>
+        <v>0.2232493003700316</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05559015057568738</v>
+        <v>0.0526043510334744</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2946090801618906</v>
+        <v>0.1706449493365572</v>
       </c>
       <c r="E5" t="n">
-        <v>529.9663287667713</v>
+        <v>324.3932222031757</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6356219820564267</v>
+        <v>0.1571530541608961</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06824516281968585</v>
+        <v>0.0471347117581036</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5673768192367409</v>
+        <v>0.1100183424027925</v>
       </c>
       <c r="E6" t="n">
-        <v>831.3802704754874</v>
+        <v>233.4125706918696</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9380033154877552</v>
+        <v>0.1912972770059393</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07107668011768763</v>
+        <v>0.08207253470140025</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8669266353700675</v>
+        <v>0.109224742304539</v>
       </c>
       <c r="E7" t="n">
-        <v>1219.706145439861</v>
+        <v>133.0831839200837</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6790205723408407</v>
+        <v>0.1018547132303556</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2370728179437773</v>
+        <v>0.02612917179188456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4419477543970634</v>
+        <v>0.07572554143847099</v>
       </c>
       <c r="E8" t="n">
-        <v>186.4185688727389</v>
+        <v>289.812252916453</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1015459074801979</v>
+        <v>0.2817040233256696</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1226594009302523</v>
+        <v>0.01066422205198562</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02111349345005446</v>
+        <v>0.271039801273684</v>
       </c>
       <c r="E9" t="n">
-        <v>17.21310661060557</v>
+        <v>2541.580623063057</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.159709008950557</v>
+        <v>0.0718983568649836</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02702034973559005</v>
+        <v>0.3003681721653985</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1326886592149669</v>
+        <v>0.2284698153004149</v>
       </c>
       <c r="E10" t="n">
-        <v>491.0693625856185</v>
+        <v>76.06325718645297</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3253835697184519</v>
+        <v>0.1373887590192664</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03192636358403752</v>
+        <v>0.2461527283708068</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2934572061344145</v>
+        <v>0.1087639693515404</v>
       </c>
       <c r="E11" t="n">
-        <v>919.1689036616015</v>
+        <v>44.18556319542284</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06115211922877228</v>
+        <v>0.7111723219569965</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07680834807784448</v>
+        <v>0.2451991711453783</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0156562288490722</v>
+        <v>0.4659731508116182</v>
       </c>
       <c r="E12" t="n">
-        <v>20.38349898269491</v>
+        <v>190.0386321189248</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02682549469705131</v>
+        <v>0.8074025319937403</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01020283384938109</v>
+        <v>0.7774296363267867</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0370283285464324</v>
+        <v>0.0299728956669536</v>
       </c>
       <c r="E13" t="n">
-        <v>362.9219988589598</v>
+        <v>3.855383724316205</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004225746978660266</v>
+        <v>-1.869819539744805e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.004485641729012531</v>
+        <v>0.0001141245476593582</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0002598947503522648</v>
+        <v>0.0001328227430568062</v>
       </c>
       <c r="E14" t="n">
-        <v>5.793925731324022</v>
+        <v>116.3840258567849</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2697271548074719</v>
+        <v>1.399056367830154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3107473177365188</v>
+        <v>0.7810834903898229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04102016292904687</v>
+        <v>0.6179728774403306</v>
       </c>
       <c r="E2" t="n">
-        <v>13.20048817406935</v>
+        <v>79.1173907839113</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7147919720935522</v>
+        <v>0.6733814530156066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4570885838847862</v>
+        <v>0.5265112599001055</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2577033882087659</v>
+        <v>0.1468701931155011</v>
       </c>
       <c r="E3" t="n">
-        <v>56.37930967747001</v>
+        <v>27.89497667027418</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9648840427475359</v>
+        <v>0.3815131892610398</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7823380276949019</v>
+        <v>0.5025577319423724</v>
       </c>
       <c r="D4" t="n">
-        <v>0.182546015052634</v>
+        <v>0.1210445426813326</v>
       </c>
       <c r="E4" t="n">
-        <v>23.33339408164673</v>
+        <v>24.08569901282758</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2232493003700316</v>
+        <v>0.2050960479753876</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0526043510334744</v>
+        <v>0.3142462885412678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1706449493365572</v>
+        <v>0.1091502405658803</v>
       </c>
       <c r="E5" t="n">
-        <v>324.3932222031757</v>
+        <v>34.73397922137951</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1571530541608961</v>
+        <v>0.3375598574414406</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0471347117581036</v>
+        <v>0.1280147895452361</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1100183424027925</v>
+        <v>0.2095450678962045</v>
       </c>
       <c r="E6" t="n">
-        <v>233.4125706918696</v>
+        <v>163.6881712188094</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1912972770059393</v>
+        <v>0.241129323648149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08207253470140025</v>
+        <v>0.3207723830368643</v>
       </c>
       <c r="D7" t="n">
-        <v>0.109224742304539</v>
+        <v>0.0796430593887153</v>
       </c>
       <c r="E7" t="n">
-        <v>133.0831839200837</v>
+        <v>24.82852751683502</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1018547132303556</v>
+        <v>0.2303340195085497</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02612917179188456</v>
+        <v>0.2418381364586348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07572554143847099</v>
+        <v>0.01150411695008513</v>
       </c>
       <c r="E8" t="n">
-        <v>289.812252916453</v>
+        <v>4.756949056317612</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2817040233256696</v>
+        <v>0.2831993416462108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01066422205198562</v>
+        <v>0.2217313023366659</v>
       </c>
       <c r="D9" t="n">
-        <v>0.271039801273684</v>
+        <v>0.06146803930954486</v>
       </c>
       <c r="E9" t="n">
-        <v>2541.580623063057</v>
+        <v>27.72185914292552</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0718983568649836</v>
+        <v>0.2593467844261907</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3003681721653985</v>
+        <v>0.2032442194638128</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2284698153004149</v>
+        <v>0.05610256496237792</v>
       </c>
       <c r="E10" t="n">
-        <v>76.06325718645297</v>
+        <v>27.60352304748666</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1373887590192664</v>
+        <v>-0.5833616010336651</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2461527283708068</v>
+        <v>-0.6963084259726409</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1087639693515404</v>
+        <v>0.1129468249389758</v>
       </c>
       <c r="E11" t="n">
-        <v>44.18556319542284</v>
+        <v>-16.22080398943983</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7111723219569965</v>
+        <v>0.05161704172891367</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2451991711453783</v>
+        <v>-0.009007976017924912</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4659731508116182</v>
+        <v>0.06062501774683858</v>
       </c>
       <c r="E12" t="n">
-        <v>190.0386321189248</v>
+        <v>-673.0148662274549</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8074025319937403</v>
+        <v>0.1322363993951733</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7774296363267867</v>
+        <v>0.1280811802270394</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0299728956669536</v>
+        <v>0.004155219168133939</v>
       </c>
       <c r="E13" t="n">
-        <v>3.855383724316205</v>
+        <v>3.244207432167872</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.869819539744805e-05</v>
+        <v>0.0001561526445396481</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001141245476593582</v>
+        <v>0.0001350944481873446</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001328227430568062</v>
+        <v>2.105819635230349e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>116.3840258567849</v>
+        <v>15.5877585162498</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Log_like</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Abs Error</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%)</t>
         </is>
@@ -462,16 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.399056367830154</v>
+        <v>0.8109331622242825</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7810834903898229</v>
+        <v>0.5128314427850377</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6179728774403306</v>
+        <v>0.07255317691507548</v>
       </c>
       <c r="E2" t="n">
-        <v>79.1173907839113</v>
+        <v>24312.43099461202</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2981017194392448</v>
+      </c>
+      <c r="G2" t="n">
+        <v>58.12859637083512</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6733814530156066</v>
+        <v>0.7182744603507193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5265112599001055</v>
+        <v>0.5623051082037978</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1468701931155011</v>
+        <v>0.05960008943057819</v>
       </c>
       <c r="E3" t="n">
-        <v>27.89497667027418</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1559693521469215</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27.73749515545805</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3815131892610398</v>
+        <v>0.6898693175195655</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5025577319423724</v>
+        <v>0.4825650783933524</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1210445426813326</v>
+        <v>0.01600158033804212</v>
       </c>
       <c r="E4" t="n">
-        <v>24.08569901282758</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.207304239126213</v>
+      </c>
+      <c r="G4" t="n">
+        <v>42.95881496779871</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2050960479753876</v>
+        <v>0.04192525587677198</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3142462885412678</v>
+        <v>0.08926669759242474</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1091502405658803</v>
+        <v>0.03884660864843816</v>
       </c>
       <c r="E5" t="n">
-        <v>34.73397922137951</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04734144171565276</v>
+      </c>
+      <c r="G5" t="n">
+        <v>53.03371021050318</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3375598574414406</v>
+        <v>0.0921460768630703</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1280147895452361</v>
+        <v>0.2162160199918205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2095450678962045</v>
+        <v>0.04509315982452306</v>
       </c>
       <c r="E6" t="n">
-        <v>163.6881712188094</v>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1240699431287502</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57.38240077374646</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.241129323648149</v>
+        <v>0.2277103899664046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3207723830368643</v>
+        <v>0.08450414923150762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0796430593887153</v>
+        <v>0.01370690322584272</v>
       </c>
       <c r="E7" t="n">
-        <v>24.82852751683502</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.143206240734897</v>
+      </c>
+      <c r="G7" t="n">
+        <v>169.4665197356985</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2303340195085497</v>
+        <v>0.2261970506325413</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2418381364586348</v>
+        <v>0.2614854172694429</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01150411695008513</v>
+        <v>0.006069183299760277</v>
       </c>
       <c r="E8" t="n">
-        <v>4.756949056317612</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0352883666369016</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.49534784975766</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +647,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2831993416462108</v>
+        <v>0.34573735106498</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2217313023366659</v>
+        <v>0.3973327631386137</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06146803930954486</v>
+        <v>0.01851585358497113</v>
       </c>
       <c r="E9" t="n">
-        <v>27.72185914292552</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05159541207363366</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.98544113656041</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +672,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2593467844261907</v>
+        <v>0.3401652313497971</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2032442194638128</v>
+        <v>0.0716825736498875</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05610256496237792</v>
+        <v>0.01388695725330142</v>
       </c>
       <c r="E10" t="n">
-        <v>27.60352304748666</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2684826576999096</v>
+      </c>
+      <c r="G10" t="n">
+        <v>374.5438312681607</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +697,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5833616010336651</v>
+        <v>0.1725816787490486</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.6963084259726409</v>
+        <v>-0.5740689657968703</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1129468249389758</v>
+        <v>0.278241389980415</v>
       </c>
       <c r="E11" t="n">
-        <v>-16.22080398943983</v>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7466506445459189</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-130.0628825161253</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +722,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05161704172891367</v>
+        <v>-0.03417644598324221</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.009007976017924912</v>
+        <v>0.1774805389478946</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06062501774683858</v>
+        <v>0.2331555552538416</v>
       </c>
       <c r="E12" t="n">
-        <v>-673.0148662274549</v>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2116569849311368</v>
+      </c>
+      <c r="G12" t="n">
+        <v>119.2564470368641</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +747,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1322363993951733</v>
+        <v>-0.4501122718862748</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1280811802270394</v>
+        <v>-0.1821106890830875</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004155219168133939</v>
+        <v>0.1619736121702256</v>
       </c>
       <c r="E13" t="n">
-        <v>3.244207432167872</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2680015828031873</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-147.1641143924903</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +772,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0001561526445396481</v>
+        <v>0.0005739705166805716</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001350944481873446</v>
+        <v>0.0002708716708733863</v>
       </c>
       <c r="D14" t="n">
-        <v>2.105819635230349e-05</v>
+        <v>7.539299047881642e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>15.5877585162498</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0003030988458071854</v>
+      </c>
+      <c r="G14" t="n">
+        <v>111.8975804409104</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ec18ff9d9d96f3/KU^J MAT-OEK/Kandidat/Thesis/Thesis_linear_CDS/Simulation_studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_085DDA57D45B4E0F6235547658C95E3C876382B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0854FD5B-2A8C-4373-A004-89AEDC1AA8C3}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_085DF99F9758A00E6235547658238E7C8DC983A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D983A9-1CC3-40DC-86BC-5BD06732736F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,9 @@
     <t>Parameter</t>
   </si>
   <si>
+    <t>True</t>
+  </si>
+  <si>
     <t>SE</t>
   </si>
   <si>
@@ -77,9 +80,6 @@
   </si>
   <si>
     <t>LogLike</t>
-  </si>
-  <si>
-    <t>True</t>
   </si>
 </sst>
 </file>
@@ -451,321 +451,321 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>0.83027970882590962</v>
+        <v>1.623216485667669</v>
       </c>
       <c r="C2">
-        <v>1.1863557545576069</v>
+        <v>1.072839344173294</v>
       </c>
       <c r="D2">
-        <v>2.0235556197722961E-2</v>
+        <v>0.21409308513863021</v>
       </c>
       <c r="E2">
-        <v>28044.402157328681</v>
+        <v>24674.460923635099</v>
       </c>
       <c r="F2">
-        <v>0.35607604573169699</v>
+        <v>0.550377141494375</v>
       </c>
       <c r="G2">
-        <v>30.014272225153761</v>
+        <v>51.300984111324077</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>1.2828002210121909</v>
+        <v>1.457094869802497</v>
       </c>
       <c r="C3">
-        <v>1.32653113991076</v>
+        <v>1.843437656927255</v>
       </c>
       <c r="D3">
-        <v>1.644390740971351E-2</v>
+        <v>0.1530278698212105</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>4.373091889856906E-2</v>
+        <v>0.38634278712475822</v>
       </c>
       <c r="G3">
-        <v>3.296637190251785</v>
+        <v>20.957735439165109</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>0.38930106051953711</v>
+        <v>0.69701631474103454</v>
       </c>
       <c r="C4">
-        <v>1.100601055447832</v>
+        <v>0.6798106592094475</v>
       </c>
       <c r="D4">
-        <v>2.7541846012968528E-3</v>
+        <v>6.0145823797679203E-3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.71129999492829454</v>
+        <v>1.7205655531587039E-2</v>
       </c>
       <c r="G4">
-        <v>64.628322079781086</v>
+        <v>2.5309481836597731</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>0.91885049302651101</v>
+        <v>0.53864433390858124</v>
       </c>
       <c r="C5">
-        <v>0.28292314829021092</v>
+        <v>0.77770920795026666</v>
       </c>
       <c r="D5">
-        <v>6.5501738164813889E-3</v>
+        <v>2.196824110035835</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.63592734473630008</v>
+        <v>0.23906487404168539</v>
       </c>
       <c r="G5">
-        <v>224.7703479122861</v>
+        <v>30.739622418997161</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0.20351674866432379</v>
+        <v>0.56863927696077243</v>
       </c>
       <c r="C6">
-        <v>0.57588312305804734</v>
+        <v>0.28955489524110661</v>
       </c>
       <c r="D6">
-        <v>2.8204833994943208E-3</v>
+        <v>1.5449960600703121</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3723663743937235</v>
+        <v>0.27908438171966587</v>
       </c>
       <c r="G6">
-        <v>64.660060259517294</v>
+        <v>96.383927989640071</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>0.31768028331246362</v>
+        <v>0.26982362171967161</v>
       </c>
       <c r="C7">
-        <v>0.27193265207270989</v>
+        <v>0.35781771008591728</v>
       </c>
       <c r="D7">
-        <v>2.4211335855746242E-3</v>
+        <v>0.36734776527412022</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>4.5747631239753672E-2</v>
+        <v>8.7994088366245782E-2</v>
       </c>
       <c r="G7">
-        <v>16.823147529749971</v>
+        <v>24.591876222425409</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>0.97899896067645553</v>
+        <v>8.9659398764096204E-2</v>
       </c>
       <c r="C8">
-        <v>0.70780618698037678</v>
+        <v>8.8847918675990151E-2</v>
       </c>
       <c r="D8">
-        <v>1.918982559226267E-2</v>
+        <v>4.3302743707466264E-3</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.27119277369607869</v>
+        <v>8.1148008810605354E-4</v>
       </c>
       <c r="G8">
-        <v>38.314552582965383</v>
+        <v>0.91333606931790079</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>0.72157211346561612</v>
+        <v>0.19858902177337001</v>
       </c>
       <c r="C9">
-        <v>0.99568609957678889</v>
+        <v>3.2924103935205369E-3</v>
       </c>
       <c r="D9">
-        <v>1.709310706205204E-2</v>
+        <v>0.40522260115399888</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.27411398611117282</v>
+        <v>0.19529661137984941</v>
       </c>
       <c r="G9">
-        <v>27.53016098423825</v>
+        <v>5931.7213845574397</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>0.248368462851146</v>
+        <v>0.46320242146556267</v>
       </c>
       <c r="C10">
-        <v>0.1929122660289134</v>
+        <v>0.30315779341772608</v>
       </c>
       <c r="D10">
-        <v>5.8943939363845354E-3</v>
+        <v>0.31549204359628458</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>5.5456196822232573E-2</v>
+        <v>0.16004462804783659</v>
       </c>
       <c r="G10">
-        <v>28.746848483922161</v>
+        <v>52.792516479135507</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-0.8309930763767237</v>
+        <v>0.37310587366376757</v>
       </c>
       <c r="C11">
-        <v>-0.38444116023902131</v>
+        <v>0.92401167169187948</v>
       </c>
       <c r="D11">
-        <v>0.85270301210057942</v>
+        <v>3.7190667779032169E-2</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.4465519161377024</v>
+        <v>0.5509057980281119</v>
       </c>
       <c r="G11">
-        <v>-116.1561149852072</v>
+        <v>59.621086497684061</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>0.24918397944130161</v>
+        <v>0.59666762952793417</v>
       </c>
       <c r="C12">
-        <v>0.75346360075002061</v>
+        <v>-0.43706779148793018</v>
       </c>
       <c r="D12">
-        <v>0.51678704685816401</v>
+        <v>6.7200247339504374E-2</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.50427962130871906</v>
+        <v>1.033735421015864</v>
       </c>
       <c r="G12">
-        <v>66.928199425525506</v>
+        <v>-236.51603736268709</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>-0.1455267218022491</v>
+        <v>0.48321864685192339</v>
       </c>
       <c r="C13">
-        <v>0.1588423164623689</v>
+        <v>0.43661136534610578</v>
       </c>
       <c r="D13">
-        <v>0.17986041215170009</v>
+        <v>5.3044820011867853E-2</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0.30436903826461797</v>
+        <v>4.660728150581761E-2</v>
       </c>
       <c r="G13">
-        <v>191.61709866950071</v>
+        <v>10.67477514445177</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>2.990673487753507E-4</v>
+        <v>4.3677111129711819E-4</v>
       </c>
       <c r="C14">
-        <v>2.7087167087338631E-4</v>
+        <v>3.813029473349604E-4</v>
       </c>
       <c r="D14">
-        <v>2.4522959644541498E-6</v>
+        <v>6.0919256086608964E-6</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2.8195677901964449E-5</v>
+        <v>5.5468163962157787E-5</v>
       </c>
       <c r="G14">
-        <v>10.409238371458921</v>
+        <v>14.547006350158391</v>
       </c>
     </row>
   </sheetData>
